--- a/publications-review.xlsx
+++ b/publications-review.xlsx
@@ -571,7 +571,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -629,7 +629,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -687,7 +687,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -807,7 +807,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -869,7 +869,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -927,7 +927,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -989,7 +989,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1089,11 +1089,10 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=2YQxaJgAAAAJ&amp;pagesize=100&amp;sortby=pubdate&amp;citation_for_view=2YQxaJgAAAAJ:HoB7MX3m0LUC</t>
@@ -1147,7 +1146,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1202,10 +1201,14 @@
           <t>121977</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Additive Manufacture</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1263,7 +1266,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1325,7 +1328,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1376,10 +1379,14 @@
           <t>114726</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Stainless Steel Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1441,7 +1448,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1503,7 +1510,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1561,7 +1568,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1623,7 +1630,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -1678,10 +1685,14 @@
           <t>121041</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Built-Up Section Members</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
@@ -1735,7 +1746,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
@@ -1793,7 +1804,7 @@
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
@@ -1844,10 +1855,14 @@
           <t>114166</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Built-Up Section Members</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
@@ -1898,10 +1913,14 @@
           <t>114119</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Additive Manufacture</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
@@ -1963,7 +1982,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
@@ -2021,7 +2040,7 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
@@ -2079,7 +2098,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
@@ -2134,10 +2153,14 @@
           <t>113427</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Built-Up Section Members</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
@@ -2195,7 +2218,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
@@ -2250,10 +2273,14 @@
           <t>113381</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Built-Up Section Members</t>
+        </is>
+      </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
@@ -2304,10 +2331,14 @@
           <t>113873</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Aluminium Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
@@ -2365,7 +2396,7 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
@@ -2416,10 +2447,14 @@
           <t>113745</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / High Strength Steel Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr"/>
@@ -2474,10 +2509,14 @@
           <t>120261</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Built-Up Section Members</t>
+        </is>
+      </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
@@ -2532,10 +2571,14 @@
           <t>120192</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Additive Manufacture</t>
+        </is>
+      </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr"/>
@@ -2590,10 +2633,14 @@
           <t>113190</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Stainless Steel Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
@@ -2648,10 +2695,14 @@
           <t>120177</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Aluminium Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
@@ -2709,7 +2760,7 @@
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
@@ -2759,7 +2810,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
@@ -2817,7 +2868,7 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
@@ -2879,7 +2930,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
@@ -2934,10 +2985,14 @@
           <t>112871</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Built-Up Section Members</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr"/>
@@ -2999,7 +3054,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr"/>
@@ -3054,10 +3109,14 @@
           <t>119450</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Aluminium Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr"/>
@@ -3112,10 +3171,14 @@
           <t>119521</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / Stainless Steel Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr"/>
@@ -3170,10 +3233,14 @@
           <t>109168</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Anti-Seismic Devices / Plate Dampers</t>
+        </is>
+      </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr"/>
@@ -3231,7 +3298,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
@@ -3293,7 +3360,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr"/>
@@ -3355,7 +3422,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr"/>
@@ -3409,7 +3476,7 @@
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr"/>
@@ -3471,7 +3538,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr"/>
@@ -3530,10 +3597,14 @@
           <t>957-971</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Anti-Seismic Devices / BRBs</t>
+        </is>
+      </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr"/>
@@ -3595,7 +3666,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr"/>
@@ -3657,7 +3728,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr"/>
@@ -3719,7 +3790,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
@@ -3781,7 +3852,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
@@ -3843,7 +3914,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr"/>
@@ -3905,7 +3976,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr"/>
@@ -3967,7 +4038,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr"/>
@@ -4029,7 +4100,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr"/>
@@ -4091,7 +4162,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr"/>
@@ -4153,7 +4224,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr"/>
@@ -4215,7 +4286,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr"/>
@@ -4277,7 +4348,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr"/>
@@ -4339,7 +4410,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr"/>
@@ -4401,7 +4472,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr"/>
@@ -4463,7 +4534,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr"/>
@@ -4525,7 +4596,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr"/>
@@ -4587,7 +4658,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr"/>
@@ -4649,7 +4720,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr"/>
@@ -4711,7 +4782,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr"/>
@@ -4773,7 +4844,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr"/>
@@ -4835,7 +4906,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr"/>
@@ -4890,10 +4961,14 @@
           <t>109545</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>High-Performance Structures / High Strength Steel Connections &amp; Members</t>
+        </is>
+      </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr"/>
@@ -4955,7 +5030,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr"/>
@@ -5017,7 +5092,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr"/>
@@ -5079,7 +5154,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr"/>
@@ -5145,7 +5220,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr"/>
@@ -5207,7 +5282,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr"/>
@@ -5257,7 +5332,7 @@
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
@@ -5319,7 +5394,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr"/>
@@ -5381,7 +5456,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr"/>
@@ -5443,7 +5518,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr"/>
@@ -5505,7 +5580,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr"/>
@@ -5567,7 +5642,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr"/>
@@ -5629,7 +5704,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr"/>
@@ -6013,7 +6088,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6038,7 +6113,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6059,15 +6134,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Journal of Constructional Steel Research</t>
+          <t>Structures</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6084,15 +6159,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Structures</t>
+          <t>Journal of Constructional Steel Research</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6113,7 +6188,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6134,46 +6209,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Earthquakes and Structures</t>
+          <t>Journal of Structural Engineering</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Journal of Structural Engineering</t>
+          <t>Earthquakes and Structures</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6259,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6205,7 +6280,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -6222,7 +6297,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -6235,7 +6310,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advances in Structural Engineering</t>
+          <t>Earthquake Engineering &amp; Structural Dynamics</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6243,20 +6318,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Automation in Construction</t>
+          <t>Composite Structures</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6264,20 +6339,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Composite Structures</t>
+          <t>Construction and Building Materials</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6285,20 +6360,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Construction and Building Materials</t>
+          <t>Automation in Construction</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6306,20 +6381,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Earthquake Engineering &amp; Structural Dynamics</t>
+          <t>Advances in Structural Engineering</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6327,20 +6402,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineering Failure Analysis</t>
+          <t>International Journal of Steel Structures</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6348,20 +6423,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>International Journal of Steel Structures</t>
+          <t>Engineering Failure Analysis</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6369,13 +6444,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -6396,13 +6471,13 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
